--- a/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,52; 92,7</t>
+          <t>85,35; 92,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,37; 92,31</t>
+          <t>87,41; 92,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,52; 91,63</t>
+          <t>87,76; 91,88</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,27; 78,86</t>
+          <t>72,5; 78,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,77; 87,45</t>
+          <t>71,98; 87,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,6; 82,89</t>
+          <t>73,56; 83,6</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,41; 69,9</t>
+          <t>57,9; 69,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,74; 73,16</t>
+          <t>64,9; 73,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,92; 70,06</t>
+          <t>62,97; 70,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,07; 77,78</t>
+          <t>72,91; 77,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,98; 85,43</t>
+          <t>75,06; 85,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,15; 81,34</t>
+          <t>75,0; 81,8</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>218294; 236627</t>
+          <t>217875; 236128</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>333062; 351909</t>
+          <t>333216; 352110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>557068; 583237</t>
+          <t>558567; 584786</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>777004; 847824</t>
+          <t>779399; 846015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>874688; 1051148</t>
+          <t>865249; 1051423</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1675969; 1887546</t>
+          <t>1675054; 1903752</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>189125; 226345</t>
+          <t>187495; 224918</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>208881; 236033</t>
+          <t>209408; 238040</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>406724; 452942</t>
+          <t>407101; 452495</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1208685; 1286556</t>
+          <t>1206035; 1289230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1428956; 1628198</t>
+          <t>1430633; 1631355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2675239; 2895720</t>
+          <t>2669927; 2912161</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,35; 92,5</t>
+          <t>85,0; 92,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,41; 92,37</t>
+          <t>87,6; 92,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,76; 91,88</t>
+          <t>87,89; 91,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,5; 78,69</t>
+          <t>73,06; 79,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,98; 87,47</t>
+          <t>74,39; 79,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,56; 83,6</t>
+          <t>74,47; 78,28</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,9; 69,46</t>
+          <t>56,81; 67,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,9; 73,78</t>
+          <t>65,22; 73,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,97; 70,0</t>
+          <t>62,67; 69,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,91; 77,94</t>
+          <t>73,38; 77,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,06; 85,6</t>
+          <t>76,81; 80,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,0; 81,8</t>
+          <t>75,81; 78,52</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>228403</t>
+          <t>261300</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>377908</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572293</t>
+          <t>639208</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>217875; 236128</t>
+          <t>248335; 270953</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>333216; 352110</t>
+          <t>366552; 387075</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>558567; 584786</t>
+          <t>624564; 653186</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>813869</t>
+          <t>885313</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>946313</t>
+          <t>824392</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1760182</t>
+          <t>1709705</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>779399; 846015</t>
+          <t>847679; 916851</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>865249; 1051423</t>
+          <t>797648; 847394</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1675054; 1903752</t>
+          <t>1662522; 1747688</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>216773</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>223041</t>
+          <t>253496</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429972</t>
+          <t>470269</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187495; 224918</t>
+          <t>196940; 234143</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>209408; 238040</t>
+          <t>237158; 267805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>407101; 452495</t>
+          <t>445120; 493698</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1249203</t>
+          <t>1363386</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1513243</t>
+          <t>1455796</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2762446</t>
+          <t>2819183</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1206035; 1289230</t>
+          <t>1320228; 1400284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1430633; 1631355</t>
+          <t>1424310; 1485808</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2669927; 2912161</t>
+          <t>2769695; 2868857</t>
         </is>
       </c>
     </row>
